--- a/data/raw/김포 26년/항공통계상세조회(노선) (2).xlsx
+++ b/data/raw/김포 26년/항공통계상세조회(노선) (2).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>9908</t>
-  </si>
-  <si>
-    <t>1801765</t>
-  </si>
-  <si>
-    <t>15641</t>
+    <t>4955</t>
+  </si>
+  <si>
+    <t>905463</t>
+  </si>
+  <si>
+    <t>7048</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,181 +53,169 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>560</t>
-  </si>
-  <si>
-    <t>98858</t>
-  </si>
-  <si>
-    <t>1009</t>
+    <t>280</t>
+  </si>
+  <si>
+    <t>47895</t>
+  </si>
+  <si>
+    <t>466</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>6768</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>642</t>
+  </si>
+  <si>
+    <t>98233</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>8482</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>5138</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>72041</t>
+  </si>
+  <si>
+    <t>1278</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>13455</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>6684</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>9938</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>10845</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>10388</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3015</t>
+  </si>
+  <si>
+    <t>584159</t>
+  </si>
+  <si>
+    <t>3910</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>8462</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2315</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>13642</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1286</t>
-  </si>
-  <si>
-    <t>195563</t>
-  </si>
-  <si>
-    <t>773</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>17951</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>10230</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>664</t>
-  </si>
-  <si>
-    <t>145594</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>26794</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>13283</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>19418</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>21986</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>20903</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6027</t>
-  </si>
-  <si>
-    <t>1155432</t>
-  </si>
-  <si>
-    <t>9566</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>16968</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>타이페이(TPE)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>4420</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>40537</t>
-  </si>
-  <si>
-    <t>706</t>
+    <t>20660</t>
+  </si>
+  <si>
+    <t>284</t>
   </si>
 </sst>
 </file>
@@ -278,7 +266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -512,13 +500,13 @@
         <v>46</v>
       </c>
       <c r="D12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>48</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -529,16 +517,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>36</v>
       </c>
       <c r="E13" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s" s="0">
         <v>51</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -619,26 +607,6 @@
       </c>
       <c r="F17" t="s" s="0">
         <v>67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
